--- a/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/Test Results/Excel/Automation_Test_Report.xlsx
@@ -31940,7 +31940,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 23:40:55</t>
+          <t>2026-10-15 23:50:37</t>
         </is>
       </c>
     </row>
